--- a/regulatory-compliance/cloud-foundation/9.1/eu-nis2/vcf-91-companion-eu-nis2.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/eu-nis2/vcf-91-companion-eu-nis2.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -975,15 +990,15 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
+          <t>VCF provides technical capabilities that support an organization's incident response operations, though it does not govern organization-wide incident response processes or maintain incident response documentation. VCF Operations is the primary platform for detecting, tracking, and investigating infrastructure-level incidents across the VCF environment.
+VCF Operations includes a dedicated incident management system that displays all incidents with their current status and key metadata. Each incident record tracks state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation. Operators can edit, share, and delete incidents directly from the incident list interface, and the system maintains an audit trail of who created each incident and when. This structured tracking provides the documentation trail that incident response processes require.
+For incident investigation, VCF Operations provides root cause analysis tooling through its Troubleshooting Incident Page. This interface displays information about the affected entity, including traffic and flow data, any past incidents created for the same entity, and root cause metrics. Investigators can flag individual metrics and mark specific metrics as the root cause of an incident. The system also allows drill-down into related entities to view detailed metrics for problem investigation, supporting a methodical approach to identifying the source and scope of an issue. A summary view displays the count of in-progress incidents, entity counts, and top root causes, which supports situational awareness during active incident response and helps teams prioritize efforts across multiple concurrent issues.
+For detection, VCF Operations performs event correlation across monitored systems, correlating a subset of published events and delivering them as faults. The platform maps events from target systems into the VCF Operations severity model, with event severity ranked from Info to Immediate. This automated correlation and severity classification helps operations teams identify incidents that require immediate response. Notification rules can be configured to trigger actions based on incident state changes, with configurable fields including incident state, resolution code, on-hold reason, impact, urgency, priority, assignment group, assigned-to person, severity, approval actions, related problems, and change cause. VCF Operations also supports defining fault symptoms and metric event symptoms based on thresholds and conditions reported by monitored systems, which can be combined into alert definitions that surface conditions requiring operator attention.
+At the VMware vCenter level, alarms can execute scripts, send SNMP traps, or call APIs when infrastructure conditions match defined thresholds. The SNMP agent included with vCenter sends traps when alarms are triggered, and VCF PowerCLI provides programmatic access to alarm management through cmdlets that support creation of script-based and SNMP alarm actions. These capabilities provide automated event detection and alerting that feed into broader incident response processes.
+To integrate with broader organizational incident response workflows, VCF Operations supports a ServiceNow Notifications plug-in that creates incidents directly in a ServiceNow ticketing system. The integration is configurable with fields including caller ID, incident category, sub-category, business service, contact type, and propagation settings for alert updates. This integration enables VCF-detected incidents to flow into an organization's established incident response and ticketing processes.
+For recovery, vSphere HA automatically restarts VMs on healthy hosts after a physical machine failure. Proactive HA integrates with hardware vendor health monitoring to evacuate workloads before failures occur. vSphere cluster HA configuration supports multiple remediation modes, including quarantine mode, maintenance mode, and mixed mode. These recovery capabilities can be exercised ad hoc or incorporated into existing playbooks and runbooks.
+VMware vDefend (a separate product that extends VCF's networking foundation) adds automated threat detection and containment through IDS/IPS and network detection features, including quarantine policies that isolate affected VMs while preserving forensic access.
+This control requires organization-wide incident response governance, documented processes, and cross-functional coordination that go beyond what any infrastructure platform provides on its own. VCF delivers incident tracking, investigation tooling, event correlation, automated alerting, ITSM integration, and infrastructure recovery capabilities that form a technical foundation for incident response, but organizations must build their own incident response plans, escalation procedures, communication protocols, and training programs around these capabilities.</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -993,12 +1008,12 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1008,11 +1023,9 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
+          <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
@@ -1104,11 +1117,14 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+          <t>VCF Protection and Recovery (PNR) provides mechanisms for secure recovery and reconstitution of virtual machine workloads to a known state after a disruption, compromise, or failure.
+Recovery is organized through protection groups and recovery plans. Protection groups define which virtual machines are protected, while recovery plans orchestrate the sequence of steps required to recover those workloads at the recovery site. The state of a recovery plan is determined by the states of the protection groups within it, and the plan state governs which operations are permitted at each stage of the DR lifecycle. Recovery plans support two primary modes: planned migration for orderly, scheduled failover, and disaster recovery for unplanned site failures. A single recovery plan can also be configured to serve both disaster recovery and cyber recovery operations, allowing organizations to maintain consistent recovery procedures across different incident types.
+Recovery plan testing is a built-in capability. Recovery plans should be tested before use for planned migration or disaster recovery to validate their functionality. This confirms that the recovery process will bring protected virtual machines online at the recovery site and that inventory mappings correctly place workloads on the appropriate networks, storage, and compute resources.
+Cyber Recovery extends reconstitution capabilities with an Isolated Recovery Environment (IRE) designed for compromise scenarios such as ransomware incidents. The IRE provides a dedicated, isolated segment of the recovery environment that blocks direct private network connections from production, allowing compromised workloads to be analyzed and validated before being returned to production. Cyber Recovery transitions virtual machines through a controlled sequence of states, including Entering validated, Validated, Staging, and Staged, to prepare them for recovery. This state-based workflow supports data integrity validation prior to production restoration.
+Recovery plan compliance checks verify that protection groups are actively replicating, that sufficient point-in-time snapshots are available for each virtual machine in the plan, and that all workflow steps can execute without conflict. Continuous compliance monitoring provides warnings when VM configuration status deviates from expected state.
+The Configuration Import/Export Tool enables administrators to export PNR server configuration data, including inventory mappings, placeholder datastores, advanced settings, array manager configurations, and protection group definitions. This capability supports configuration backup and reconstitution of the PNR environment itself after a failure or migration.
+PNR integrates with VCF Operations for recovery plan lifecycle visibility. The Recovery Plans Details dashboard shows the current phase of the DR lifecycle, including whether a plan is ready, whether a test is in progress, and whether incomplete recovery or cleanup operations require attention. PNR also supports recovery of VCF Automation and VCF Operations services: when a disaster event affects the management domain containing these services, PNR enables service recovery in another management domain.
+All communications between PNR and VMware vCenter instances use TLS certificates and private keys. The PNR Appliance supports importing server certificates signed by a certificate authority to establish secure communications across both protected and recovery sites.</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
@@ -1118,14 +1134,11 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides a built-in backup framework for managed PostgreSQL, MySQL, and SQL Server databases, giving administrators and database owners the tools to establish recurring backup schedules aligned with organizational recovery objectives.
-Backup configuration is available at database creation and can be modified at any time through the database settings interface. Administrators activate automated backups using the Enable Automated Backups toggle (also exposed as Enable Backups in MySQL flows), specify a backup location pointing to S3-compatible object storage, and define a retention period. PostgreSQL databases support both full and incremental backups, and SQL Server databases support full and differential backup schedules. SQL Server adds a Log Backup Frequency setting in Advanced Settings with a maximum value of 30 minutes that is directly related to the Recovery Point Objective for that database. Backup schedules are expressed as cron expressions and can be customized per database or applied at the policy level.
-Data Service Policies provide centralized backup governance for databases deployed within a namespace. A policy can include named backup jobs specifying backup type and schedule, and the policy backup requirement setting offers three options: Require Automated Backups (databases must have automated backups), Allow Automated Backups (users can choose to activate or deactivate automated backups), and Disallow. Allowed backup locations are defined in the policy via the allowedBackupLocations parameter, restricting where backups can be stored. When multiple policies apply, DSM aggregates the backup schedules into a single effective backup policy per database. High Availability clusters require automated backups to be enabled in order to provision databases, helping ensure that recoverable copies exist for replicated topologies.
-DSM also supports on-demand backups for primary PostgreSQL databases, independent of the configured automated schedule, which is useful for capturing a point-in-time snapshot before a significant change. Backup storage is managed centrally through the Settings pane Storage Settings tab, which displays Database Backup Storage buckets and allows administrators to add or edit object storage targets. Provider-level control plane backups are stored in a designated Provider Backup Repo bucket configured during Provider VM setup, and recovery of the Provider VM from backup uses the restore-provider command with a pgbackrest.conf path to restore the appliance to the latest timestamp.
-DSM retains automated backups of deleted databases until the configured retention period expires. When a database with configured backups is deleted, the system automatically creates an archive containing all collected backups that remains available in the Archives tab for the remainder of the retention period, allowing recovery of inadvertently deleted databases. Administrators can also manually delete retained backups of deleted databases when they are no longer needed.
-Point-in-time recovery is supported from configured backup storage, restoring a backup at a specified date and time to a newly created database VM with a user-specified name and datastore location. The restore function is also accessible through the VCF Automation UI for tenant users. If any incremental backup in a chain is deleted, DSM cannot restore data to points in time that depended on that backup, and a restore from an incremental chain requires the last full backup plus all following incremental backups. Maintaining a balanced schedule of full and incremental backups reduces the risk of a gap in the recovery chain.
-DSM provides operational validation of the backup target through the backup storage repository alert, which checks connection and operational status, bucket name, certificate expiration date, credentials, and sufficient available space in the repository. This helps surface configuration drift or storage failures that would otherwise compromise recoverability.
-Satisfying this control fully requires that the organization define RTOs and RPOs for each database workload, configure backup policies accordingly, and periodically test restoration to verify that backup data is valid and recovery objectives are achievable. DSM provides the technical backup infrastructure and operational checks on the backup target; RTO and RPO definition and end-to-end backup integrity testing are organizational responsibilities.</t>
+          <t>VMware Data Services Manager (DSM) provides several mechanisms that support the secure recovery and reconstitution of database services to a known state following a disruption, compromise, or failure.
+For backup-based recovery, DSM supports point-in-time recovery (PITR), which restores a backup to a newly created database VM. During the restore operation, the administrator can specify the database name, choose the target datastore location, and configure management settings. DSM supports restoring backups from either local or cloud-compatible (S3-compatible) storage, with restoration permitted to any point in time within the configured backup retention period. When restoring a deleted database, DSM's Archives tab allows users to access databases with retained backups and create a new database VM from a selected restore point, including options to restore to the most recent available timestamp or a custom point in time. PITR coverage extends across PostgreSQL, MySQL, and SQL Server database engines. For SQL Server, DSM automatically manages the database recovery model based on backup status, using Full Recovery for databases with automated backups enabled and Simple Recovery otherwise. Cloning a MySQL or PostgreSQL database is functionally equivalent to PITR to the latest available time, giving operators an additional path for rebuilding a known-good database instance. For failed clusters, DSM supports restoration to a different cluster with the option to target either the latest available time or a specific custom restore point.
+For active recovery and failover of PostgreSQL databases, DSM provides a multi-site disaster recovery deployment model in which a secondary instance replicates from the primary across sites. When a failover is needed, DSM provides a switchover workflow that reverses the roles of instances, redirecting the secondary to become the new primary and restoring the database service to a fully operational state. DSM also provides a switchover workflow for failback, allowing operators to reverse instance roles again after the primary site is restored. DSM requires trust validation of the new primary database certificate when redirecting secondary instances during disaster recovery switchover, and operators with the DSM user role must manually establish trust between primary and secondary instances by retrieving the Certificate Authority from the primary and adding it to the Provider VM that will host the secondary. For backup-location certificates, DSM supports a Trust On First Use (TOFU) configuration that extracts and trusts certificates for specific backup locations, and at least one backup location must be configured with a trusted root certificate when a data service policy requires or allows automated backups. DSM also preserves the backing virtual machines of removed database nodes in an idle state until an instance is promoted again, maintaining infrastructure capacity for disaster recovery operations.
+The resiliency of the DSM Provider Appliance itself is supplied by the underlying VCF platform (see VCF Coverage); DSM relies on vSphere High Availability to restart the appliance on another host in the event of a host failure, and does not add a separate management-plane HA mechanism. If a DSM provider restore fails for any reason, the documented procedure is to re-deploy the appliance and then follow the recovery procedure again rather than re-attempting the restore workflow on the same appliance.
+DSM tracks recovery operations through its audit and operations interfaces. Event logs record Provider Restore Success events with timestamps, allowing operators to verify that recovery operations completed. Restore operation progress is visible in the Operations tab and Operations view, and a new entry appears in the Databases view table when a restore completes. To support integrity of recovery artifacts, the DSM Consumption Operator deployment includes Signature Verification of packages.</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
@@ -1624,11 +1637,9 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Services Platform (SSP) maintains an inventory of network-visible workloads organized into a hierarchical asset collection spanning regions, zones, environments, applications, and application tiers. The Publish Inventory Assets tab in SSP displays infrastructure asset details including asset names, asset types, IP addresses, and total VM counts for assets sourced from imported CSV files, discovered services, or published infrastructure assets, providing accurate, granular records of network-visible assets.
-Platform Inventory monitoring supports ongoing inventory accuracy through several mechanisms. Administrators can filter infrastructure assets by Name and Status, identifying assets that are timed out or out of sync. The inventory hierarchy view shows regions, zones, and VMs so administrators can verify correct definition. SSP Inventory displays assigned tags for each infrastructure asset, and environment rows can be expanded to view tag assignments and confirm hierarchy accuracy. The platform also collects and displays VM tags with their respective scopes, supporting classification and tracking. Published applications and their application types are verifiable in the Inventory &gt; Applications interface.
-SSP identifies and publishes application assets, classifying them as either critical or regular applications. Application Asset Collections represent groups of workloads delivering enterprise software functions. Security Intelligence within SSP displays application associations for compute entities, indicating the tiers within each application to which a given compute entity belongs. Administering compute entity classifications in Security Intelligence requires appropriate privileges, supporting access control over classification changes. Consistent naming conventions are recommended when preparing inventory data for import, and the Asset Prefix setting enables standardized naming during segmentation planning and monitoring.
-In disconnected mode, usage files include an asset_id field providing a unique asset identifier, supporting asset tracking in environments without continuous connectivity.
-vDefend's inventory scope is limited to network-visible workloads and does not replace enterprise-wide TAASD inventory tools, authorized software catalogs with business justification records, or data asset registries required for full AST-02 compliance.</t>
+          <t>VMware vDefend contributes to identity and access management by providing identity-aware network enforcement through Identity Firewall, which integrates with Active Directory to apply firewall policy based on authenticated user identity rather than IP address alone. Identity Firewall supports assigning Active Directory users and groups as source criteria in both distributed firewall rules and gateway firewall rules, applying to tier-0 and tier-1 gateways. This allows organizations to enforce network access policy by user or group membership rather than relying solely on IP-based controls.
+Within its management plane, the Security Services Platform implements role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. These roles govern access to security policy management, analytics, incident response, and diagnostic functions across the platform. Network Detection and Response enforces the same five-role RBAC model for triage operations such as viewing detections and campaigns, and for configuration operations including SIEM integration management. For authentication, the Security Services Platform supports Active Directory and OpenLDAP as external identity sources, with one identity source configurable at a time. The License Hub integrates with external identity providers to store and manage user and group information for access delegation.
+Centralized IAM for organizational users, including VCF SSO, MFA, and directory lifecycle management, is handled by VCF and falls outside vDefend's scope.</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -1793,47 +1804,27 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple layers of access control, identity federation, tenant isolation, and monitoring to mitigate risks associated with third-party access to infrastructure assets, applications, services, and data.
-VCF SSO integrates with federated identity providers through standards-based protocols, supporting SAML 2.0, OIDC, and AD/LDAP as authentication sources. LDAP-based directory services such as Active Directory are supported for identity management across the platform, including NSX Manager, which supports both Active Directory over LDAP and Open LDAP as identity sources. This allows organizations to extend their existing identity governance to VCF rather than maintaining separate credential stores for third-party users.
-Role-based access control enforces least-privilege principles across the platform. VCF local accounts support configurable roles such as superAdmin, and VCF Automation assigns host switch-level permissions through the Cloud Administrator group (Cloudadmin role). The administrators role in VCF Operations is restricted to specific users who need access to objects and actions across the entire environment. For Kubernetes workloads, vSphere Supervisor namespaces support role-based access control with EDIT, VIEW, and OWNER roles that grant specific privileges to users or groups. The Namespace Owner/Edit/View role scopes consumers of a vSphere Namespace to provisioning VKS clusters and vSphere Pods using kubectl, while vSphere Administrator and Supervisor Administrator roles have broader access to cluster and namespace resources. This layered role model restricts third-party access to specific workload boundaries.
-VCF Automation implements a provider-and-consumer model that separates the operators of services from the organizations that consume them. Partner services from external vendors are integrated through this model, where providers manage services and organizations consume the resulting business outcomes such as self-service provisioning of Kubernetes clusters, databases, and other resources. Service providers control the publication scope of service instances to selected organizations and decide which roles, rights bundles, and UI plug-ins to include when publishing services. Provider Consumption Organizations offer additional administrative capabilities on top of standard organizations, allowing provider administrators to provision workloads while maintaining separation from consumer tenants. This architectural separation limits third-party visibility and access to only the resources they need to operate.
-For third-party application integration, VCF Automation supports dedicated service accounts that automate access for third-party applications. Organizations can generate and issue API access tokens that applications use on their behalf, providing a controlled mechanism for programmatic access rather than requiring shared user credentials. The VCF Operations orchestrator presents an open architecture for plugging in external third-party applications, with integration points managed through the platform rather than through direct infrastructure access.
-Tenant isolation is enforced through VCF Automation Organizations, which provide secure infrastructure isolation, quotas, and chargeback across multiple tenants. Within each organization, further isolation exists at the project and namespace levels. IT teams and cloud service providers can monitor resource usage, control permissions, and provide managed services through these organizations while network isolation at the NSX segment level restricts lateral movement between tenants. An Enterprise Admin can share resources with projects in a controlled manner, making objects available for consumption only within designated boundaries. App isolation policies in VCF Automation allow deployments that require on-demand security groups to enforce vDefend firewall rules at the application level. Data-in-transit communications default to TLS encryption for platform services.
-VCF Operations monitors resource usage and policy compliance across the environment, providing visibility into third-party activity. VCF Operations supports firewall hardening that restricts network access to internal services, limiting the network paths available to third-party integrations. Service Discovery identifies permanent listening TCP ports and established UDP connections, and service discovery dashboards provide ongoing visibility into the services operating in the environment. VCF also provides capabilities to discover objects that are not compliant with a security standard, supporting ongoing risk identification for configurations affected by third-party access.
-VMware Private AI Services (PAIS) provides technical mechanisms that contribute to mitigating risks associated with third-party access to AI-related assets, services, and data. These mechanisms operate at the trust validation, authentication, authorization, and content approval layers.
-Trust Establishment for External Integrations
-PAIS uses a CA trust bundle to establish secure HTTPS communication with external services and databases. Administrators must import CA trust bundles for the OIDC provider, Private Harbor registry, content management systems used as data sources in Data Indexing and Retrieval, MCP servers providing tools for agents, and the database server when those entities are not supplied at activation. Without an explicitly configured CA trust bundle, PAIS will not establish connections to those services, so third-party integrations require deliberate administrative action rather than automatic open access. PAIS supports updating certificate content for trusted entities through the same trust bundle mechanism, allowing administrators to refresh trust material as provider certificates change.
-Access Control for Services and Data
-PAIS access is controlled through OIDC group-based authorization. User accounts must be members of specified authorized groups (configured via the authorizedGroups setting) to access the service, and the oidc-groups-claim setting controls which OIDC claim is consulted for group identification in the organization namespace. PAIS requires HTTPS-based communication for OIDC provider integration. SharePoint data sources used as Knowledge Base inputs require user name and password authentication, with support limited to SharePoint On-Premises deployments, so the credential and connectivity posture for that integration is explicit rather than implicit.
-Harbor Access and Model Storage
-The Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as a model storage backend, requiring authentication and certificate-based trust for model retrieval. These controls help administrators scope which users and workloads can push to or pull from a registry used by PAIS.
-Model Validation Before Deployment
-Before uploading a model to a PAIS Model Gallery, the platform recommends evaluating the model's performance and safety for the intended business use case, including examining inference requests for malicious behavior and performing hands-on functional tests. PAIS guidance directs administrators to distribute models within the organization that have been validated on a Deep Learning VM rather than models pulled from the Internet, which could contain malicious code or be tuned for malicious behavior. This workflow helps administrators verify third-party or externally sourced models before they become available for production use.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to mitigating risks from third-party access to organizational technology assets, applications, services, and data through network-level access controls, threat detection, and security posture reporting. Identity governance, authentication, and administrative access controls are handled by other VCF components (VMware vCenter, VCF SSO). vDefend enforces the network security boundary that constrains what third parties can reach once they have been granted access.
-vDefend enforces microsegmentation policies at the vNIC level, allowing administrators to define granular network access rules that restrict third-party workloads or connections to only the specific application tiers and services they require. Context-aware rules allow policies to incorporate workload-level attributes, limiting the network reach of third-party connections to defined sets of addresses, ports, and protocols. In multi-tenant VCF environments, the VPC Isolation with Essential Services strategy allows enterprise administrators to enforce strict inter-project isolation at the Distributed Firewall level while delegating more granular control to application owners within each project. This architecture is suited to environments where third-party development teams or external service providers operate within shared infrastructure, because Distributed Firewall policy at the project boundary can be set independently of what individual tenants configure inside their own VPCs.
-vDefend provides north-south traffic filtering at the perimeter of logical network segments. Enterprise administrators can enforce isolation between projects by denying inter-project communication except for specified infrastructure protocols, adding an enforcement point for controlling inbound and outbound access from external or third-party networks. This policy layer applies regardless of what routing exists at the NSX level, giving security teams a dedicated control plane for third-party network boundaries.
-vDefend IDS/IPS monitors east-west and north-south traffic for malicious activity, detecting exploitation attempts that may arise from compromised third-party connections. Signature rules support storing TLS and SSL certificates on disk for forensic analysis and threat investigation. Custom signature sources, including those derived from cybersecurity advisories, can be deployed to address threats specific to proprietary or custom applications that third parties introduce into the environment.
-Security Services Platform Security Segmentation capabilities identify risky application protocols, including HTTP, Telnet, FTP, TFTP, LDAP, POP3, and IMAP, in use across the environment. This flags workloads, including those operated by third parties, that transport data without encryption, and allows administrators to restrict or block them as part of the security baseline. The Security Segmentation Report identifies at-risk workloads across categories including Public Traffic, Obsolete OS, Risky Application Protocols, and Inter VDI Server Connections, providing a structured view of workload-level risk that is directly relevant to understanding the exposure introduced by third-party access. Application monitoring in Security Services Platform surfaces security risks identified across workloads, allowing administrators to take targeted remediation steps against risky or non-compliant third-party workloads.
-Security Services Platform certificate management supports importing CA bundles and web proxy certificates to establish trust for external service connections, including those used by the Malware Prevention Service. This controls which external services the platform can reach and provides a configuration point for managing trust relationships with third-party service endpoints.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -1858,16 +1849,12 @@
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides several mechanisms that allow administrators to restrict where application traffic is processed and where associated data is stored, supporting organizational requirements to control the location of information processing.
-Service Engine Group placement controls are the primary mechanism. Administrators can scope Service Engine deployment by host, cluster, or data store by configuring the Host Scope and Data Store settings under Placement Scope for each SE Group at the vCenter level. This confines traffic processing to specific physical infrastructure resources. The Data Store Scope setting in the SE Group Advanced Parameters offers three modes: Local (the Service Engine uses only storage on the physical host, keeping processed data local to that host), Shared (Avi prefers shared storage but allows specific data stores to be included or excluded), and Any (Avi determines the best available storage option).
-At the tenant level, Avi's multi-tenancy model provides additional processing location isolation. The behavior depends on tenant context: tenants in Tenant Context provide both control plane isolation and data plane isolation, fully separating application traffic between tenants. Tenants in Provider Context provide control plane isolation only. The enforce_label_group setting on a tenant further restricts access to resources tagged with specific label groups, controlling which Service Engines and resources a given tenant can access.
-In Kubernetes environments, the Avi Kubernetes Operator (AKO) CRD Operator manages namespace-scoped resources with tenant isolation for multi-tenancy support, extending processing location controls to containerized workloads. The Avi integration with VCF also allows provider administrators to define infrastructure boundaries through regions and organizations in the VCF Automation Provider Management Portal, with region quotas specifying accessible zones and capacity allocation.
-The organization is responsible for identifying processing and storage location requirements based on applicable business, regulatory, or contractual obligations, and for configuring the placement and scoping controls accordingly. Avi provides the enforcement mechanisms; defining acceptable locations and verifying that restrictions are correctly applied are organizational responsibilities.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -1899,17 +1886,18 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>VCF provides integrated mechanisms for identifying, tracking, and remediating vulnerabilities across the infrastructure stack. These capabilities span automated detection, compliance monitoring, alert-driven tracking, structured remediation workflows, and lifecycle management tooling.
-VCF Diagnostics automatically detects known issues and critical vulnerabilities within the VCF software stack, providing detailed descriptions, root cause insights, and actionable remediation steps. This capability builds on several legacy diagnostics tools and operational data to deliver integrated issue detection and remediation from a single pane. Diagnostic Findings uses a library of log and property-based diagnostic rules (also called signatures) to identify known issues across the platform, giving operations teams a structured way to discover and resolve problems.
-VCF Operations extends vulnerability tracking through compliance management, which detects violations, highlights risk areas, and provides actionable remediation recommendations. When VCF Operations detects non-compliance with a defined policy, it generates alerts or notifications. Depending on the severity, administrators can configure automated remediation actions to bring objects back into compliance without manual intervention. VCF Operations also maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation tied directly to detected conditions. To retrieve remediation recommendations for a specific virtual machine, the system must be connected to a VCF Operations instance with at least one triggered alert for that virtual machine.
-Configuration Drifts in VCF Operations provides a proactive method to monitor configuration changes across vCenter instances and vSphere clusters. Administrators can view and compare configuration drifts and identify settings that have changed over time. VCF Operations audit logging tracks each configuration change to an authenticated user who initiated the change or scheduled the job that performed the change, allowing administrators to determine who changed what and when.
-VCF lifecycle management simplifies and automates the process of applying updates and patches to software components within the VCF stack. VCF Operations includes patch planner functionality for updating or patching individual VCF core components in a VCF domain, and provides a Plan Patching capability to create patching plans for desired components. Pre-update validation runs upgrade prechecks to verify readiness before proceeding, identifying issues before the update starts. Update bundle management supports both online and offline depots; the VCF Download Tool and the lcm-bundle-transfer-util command handle bundle download, staging, and repository configuration for environments with limited or no internet connectivity.
-On the patching side, Broadcom releases security advisories for critical known vulnerabilities with step-by-step remediation instructions. Patch releases for VCF components provide time-sensitive fixes to security and catastrophic issues that affect business operations. These patches are released between major, minor, and maintenance releases and can be selectively applied based on environmental impact and operational costs.
-vSphere Lifecycle Manager (vLCM) manages desired-state configurations for ESX hosts. It can create a desired state that includes a specific version of the ESX host, compatible partner software and firmware components, and add-ons. When hosts deviate from the target specification, cluster remediation applies the desired state to each non-compliant host, with the Coordinator Manager running pre-checks to evaluate how each host is affected and whether additional steps are needed. Patches can be staged to ESX hosts before remediation begins, reducing the time hosts spend in maintenance mode during the remediation window. Remediation can also be initiated manually or scheduled as a regular task to run at a time convenient for operations teams, supporting consistent patch compliance over time. Firmware add-ons can be added, replaced, removed, upgraded, or downgraded as part of the image. The vSphere Automation REST API allows administrators to query effective global and cluster-specific remediation policies before initiating remediation, supporting a review-before-apply workflow that reduces risk during patching operations.
-VCF also provides tooling for managing remediation at scale. VCF PowerCLI supports parallel remediation with a configurable maximum number of concurrent remediations, allowing administrators to remediate multiple hosts simultaneously. Live Patching allows security updates to be applied to ESX hosts without requiring a host reboot. vCenter RDU upgrades perform automatic rollback if the upgrade fails, providing a safety net during update operations. Maintenance releases are scheduled, cumulative updates focused on platform stability and support, providing bug and security fixes, hardware enablement changes, driver updates, guest OS support, and backward-compatible new features with limited scope to minimize operational impact.
-For containerized workloads running on vSphere namespaces, VMware Kubernetes Service (VKS) extends vulnerability identification and remediation to the application layer. Harbor Registry, deployable as a standard package on VKS clusters, performs automated vulnerability scanning against container images using the Trivy vulnerability database, which can be configured to point to a custom or mirrored registry. Harbor also supports image signing to establish content trust, giving administrators a mechanism to identify images that have passed security review. Admission controls can be configured to restrict workload deployments to images sourced from a designated Harbor instance where scanning is enforced, helping constrain the image surface to scanned and trusted artifacts.
-VKS MachineHealthCheck provides automated remediation of unhealthy cluster nodes. The remediation.maxInFlight parameter controls how many concurrent node remediations may proceed simultaneously, and the triggerIf.unhealthyLessThanOrEqualTo threshold determines the condition under which remediation activates. The Kubernetes API surfaces a Remediating condition on VKS clusters, giving administrators direct visibility into the status of ongoing node remediation. DISA Security Technical Implementation Guides (STIGs) are available for both Supervisor and VKS cluster releases (VKrs), documenting known configuration weaknesses and providing step-by-step remediation guidance for hardening these deployments. The Kubernetes Security Response Committee tracks upstream Kubernetes vulnerabilities, assigns CVE identifiers, and publishes advisories through the kube-security-announce mailing list and the official Kubernetes CVE list; the committee's policy is to fully disclose vulnerabilities as soon as a user mitigation is available, with timeframes ranging from immediate to a few weeks depending on the complexity of the issue and vendor coordination requirements. Organizations running VKS can subscribe to receive these notifications and coordinate patch deployments accordingly.
-CI/CD pipelines deployed on the VCF consumption layer can incorporate Harness CI/CD with Security Testing Orchestration (STO). Harness STO integrates Wiz to perform pre-deployment vulnerability scanning across container image layers and automatically deduplicates findings, presenting each unique vulnerability, CVE, misconfiguration, or exposed secret as a single actionable item on the pipeline execution's vulnerabilities tab.</t>
+          <t>VCF provides centralized flaw remediation through VCF Operations and vSphere Lifecycle Manager, which together form a unified lifecycle management plane for all infrastructure components.
+VCF Operations is the central orchestration point for patching and update operations across the entire VCF stack. It manages update bundles with pre-update health checks and compatibility verification, and enforces component interdependency rules so that updates are applied in the correct sequence. The patch planner provides the ability to apply update or patch binaries to VCF core components, allowing administrators to select target versions for each component, including patch versions and Bill of Materials versions, giving full visibility into available releases when planning remediation. The cluster transition specification includes a remediationOptionsSpec with a configurable remediationFailureAction that supports automatic retry with adjustable retryCount and retryDelay parameters, allowing administrators to define consistent remediation behavior from a single management interface.
+VCF uses a desired-state model for host remediation through vSphere Lifecycle Manager (vLCM). Administrators define a software specification for each cluster, and vLCM brings all hosts in the cluster into compliance with that specification during remediation. This approach applies uniformly to VMware-supplied components and third-party solutions alike. To make a third-party solution available on a cluster, administrators create a software specification containing the solution and remediate all hosts in the cluster with that image, keeping all software management centralized. Hardware Support Manager (HSM) plugins, registered with vCenter, enable vendor-specific firmware and driver management alongside software updates through vSAN Proactive Hardware Management (PHM).
+The remediation workflow is coordinated through multiple layers. Before remediation begins, Coordinator Manager runs pre-checks to evaluate how each host in the cluster is affected and whether additional steps are needed. ESX Updater Manager then handles the actual remediation on each host. Coordinator Manager also allows administrators to query the status of the remediation operation for the cluster and for each individual host, providing centralized visibility into remediation progress. vSphere Lifecycle Manager also supports targeting remediation at the vCenter, data center, or folder level, processing all clusters within the targeted scope in parallel, with individual cluster failures not blocking completion of the remaining clusters.
+VCF supports programmatic management of the flaw remediation process through both the vSphere Automation REST API and PowerCLI. The REST API allows administrators to query effective global and cluster-specific remediation policies before initiating remediation, and the Update-Entity operation remediates hosts by applying baselines with configurable failure handling and retry behavior. Update Manager provides PowerCLI cmdlets for scripted workflows covering patch downloads, baseline management, and host scanning and remediation. These interfaces enable integration with external change management and orchestration systems for fully automated remediation workflows.
+At the release management level, VCF delivers patch releases that provide time-sensitive fixes to security and catastrophic issues affecting business operations. These patches are released between major, minor, and maintenance releases and are not synchronized among all components, providing a structured but flexible cadence for flaw remediation.
+For the workload consumption layer, VMware Kubernetes Service (VKS) extends centralized flaw remediation to managed Kubernetes clusters through versioned Kubernetes releases (VKrs). VKS clusters are provisioned against a specific VKr version, allowing administrators to manage the Kubernetes version lifecycle centrally across the cluster estate. Security Technical Implementation Guides (STIGs) are available for Supervisor and VKr components, providing structured hardening guidance for systematic remediation of configuration flaws. When remediation is in progress, the Kubernetes cluster condition API surfaces a Remediating status through kubectl, giving operators a centralized view of remediation state across managed clusters. At the node level, MachineHealthCheck provides automated detection and remediation of unhealthy nodes: the unhealthyLessThanOrEqualTo threshold setting controls when automated remediation is triggered relative to the count of unhealthy machines in a cluster, and the MachineDeployment remediation.maxInFlight parameter governs how many concurrent node remediations are permitted, giving operators declarative, centrally configured control over node-level flaw remediation at scale.
+Harbor, available as a VKS standard package, provides centralized vulnerability scanning of container images across the cluster estate, with content trust and policy-based replication supporting consistent and secure artifact management. Container images and other artifacts should be scanned for known vulnerabilities as part of supply chain security during the build and distribution phases of the development lifecycle.
+GitOps workflows, available through the Argo CD Supervisor Service and Harness CI/CD integration, extend centralized flaw remediation management to infrastructure automation. These pipelines maintain auditable records of configuration changes and can integrate security scanning to help identify vulnerable components before deployment. Artifactory, available as a component of CI/CD integrations, maintains version control for stored artifacts and supports rollback if a patched version introduces regressions. VKS Cluster Management Mutation Policies complement the GitOps approach by providing centralized enforcement of configuration conformance: mutation policies automate the injection of standard metadata and enforcement of resource defaults, providing a consistent operational baseline across the cluster estate. Policy enforcement follows a bottom-up hierarchy where local cluster policies take precedence, followed by project and organization inheritance. The Policy Insights page surfaces direct links to affected clusters, projects, and policies to streamline remediation, and generates Incompatibility insights when a manually installed Gatekeeper installation conflicts with cluster management policy.
+VCF Operations extends centralized remediation management in several ways. Its compliance management capabilities detect violations, highlight risk areas, and provide actionable remediation recommendations. Depending on severity, administrators can configure automated remediation actions to bring objects back into compliance. Out-of-the-box workflows are mapped to recommendations and associated with specific alerts for automated remediation. Diagnostic Findings discovers known issues using log and property-based diagnostic rules and signatures, displays affected objects and resolution recommendations with links to knowledge base articles, and integrates with VCF Log Management to provide depth and flexibility in troubleshooting.
+Configuration drift detection in VCF Operations provides scheduled drift detection for vCenter and cluster objects, comparing current values against configuration templates to proactively detect deviations from the desired state. When drift is detected, administrators can view and compare configuration changes in the Configuration Drift dashboard and take corrective action to bring systems back into compliance.
+VCF supports zero-downtime maintenance through the Distributed Resource Scheduler (DRS), which provides automatic redistribution of resources across hosts in a cluster during updates. Live Patching can update and restart discrete components without requiring full host evacuation or host reboot, and ESX Quick Boot reduces reboot time by skipping hardware initialization when the host platform supports it. Quick Boot is deactivated by default and can be enabled through the setEnableQuickBoot method via the vSphere Automation REST API, further minimizing the disruption window during remediation cycles. Patches can also be staged to host-local storage before the maintenance window begins, separating the download phase from the remediation phase to further reduce host downtime.</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -1946,11 +1934,11 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to the vulnerability remediation process primarily through its software update mechanisms and compliance tracking features. DSM does not provide vulnerability scanning or external CVE tracking; those functions require organizational processes and tools outside the platform.
-DSM supports software remediation through update bundles that apply patches to DSM appliances and managed database versions. The DSM controller manages component dependencies through status monitoring and automated remediation, helping maintain a consistent update baseline across the environment. Database engines, including PostgreSQL and MySQL, can be upgraded to new minor and major versions through the DSM interface; upgrade operations during the maintenance window may include CVE fixes, bug fixes, and performance improvements, allowing operators to remediate known vulnerabilities by updating to patched releases.
-To support issue identification, DSM surfaces database alerts with mitigation suggestions so that operators can resolve operational issues without disrupting database services. Operators should verify VM status and infrastructure health when resolving alerts to identify underlying causes. The platform can generate and download log bundles that aggregate relevant logs from database VMs to support faster diagnosis when a service faces a problem. Operators can also review active VMware vCenter infrastructure alarms through DSM troubleshooting guidance and resolve the underlying problems causing those alarms.
-Data service policies in DSM include a compliance tab that tracks whether deployed databases conform to the policy. When a data service policy is deleted, the associated services are marked as non-compliant, providing visibility into configuration drift. These policies can be enforced across different tenants, supporting consistent configuration standards across the environment.
-DSM handles the patching and software update aspects of vulnerability remediation within its own scope and provides monitoring and compliance visibility. The broader requirements of the control, including external vulnerability scanning to identify CVEs in database software, a centralized vulnerability tracking system for prioritization and assignment, and defined organizational remediation timelines and escalation procedures, must be addressed through organizational processes and tools that operate alongside DSM.</t>
+          <t>VMware Data Services Manager (DSM) provides centralized mechanisms for managing software updates to its components through the Maintenance Policy feature. Administrators configure a maintenance window specifying the time and duration during which automatic software updates are applied to DSM plug-in appliances. This window is set from the vSphere Client or the DSM UI. If the maintenance policy is edited during the 10-minute interval between automatic update attempts, the system cancels the next scheduled attempt and applies the newly configured policy, giving administrators precise control over when updates run. When automatic upgrades fail, administrators can perform manual software updates directly through the DSM interface.
+For database-level patching, DSM supports minor and major version upgrades of managed PostgreSQL, MySQL, and SQL Server databases. Minor version upgrades are applied within the configured maintenance window. The default database maintenance window is six hours starting each Saturday at 23:59, and can be reconfigured at database creation or afterward. Upgrade operations applied during the maintenance window may include CVE fixes, bug fixes, and performance improvements. In DSM, SQL Server administrators can also define maintenance windows for operating system patching of their database instances. If a PostgreSQL major version upgrade fails and data files become corrupt, DSM supports restoring the database from a backup in a separate instance.
+DSM's controller manages feature and component dependencies through status monitoring and automated remediation, reducing the need for manual intervention when dependency conditions change during or after upgrades.
+DSM also provides alerts with mitigation guidance when database-level issues are detected, enabling operators to address problems through the centralized management interface. These alerts are accessible from the DSM monitoring UI and can be forwarded to external systems via syslog for integration with broader operational workflows.
+Centralized flaw remediation at the organizational level, including vulnerability scanning across all infrastructure components, patch tracking, and governance of the remediation workflow, remains an organizational responsibility. DSM contributes to this process by providing controlled, policy-governed software update mechanisms for its own components and the database instances it manages, but it does not provide vulnerability management or patch orchestration capabilities for the broader environment.</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
@@ -1960,12 +1948,11 @@
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several mechanisms that support an organization's vulnerability identification and remediation processes for application delivery infrastructure.
-For application-layer vulnerability identification, Avi's Web Application Firewall (WAF) supports virtual patching through integration with Dynamic Application Security Testing (DAST) tools. Organizations can import scanner results into Avi to identify vulnerable application endpoints. The WAF creates Positive Security rules for each identified vulnerability, restricting requests to known-good parameters without requiring changes to the protected application. This allows organizations to limit exposure to identified vulnerabilities while application-level remediation is underway.
-In 9.1, the Avi Cloud Console adds a Live Security Threat Intelligence service, which includes an Application Rules Service providing rules targeting known application vulnerabilities identified by CVE. The service covers over 5,000 applications and automatically synchronizes rule database updates, keeping CVE-based protections current without manual rule management. When the service is temporarily unavailable, Avi Controllers continue to operate using the cached rule database.
-For tracking and documentation, the Avi Application Security Report generates a downloadable PDF documenting WAF security findings and pre-check results, supporting both technical review and organizational documentation requirements.
-The WAF Recommendation system supports the tuning portion of the vulnerability management process by proposing configuration changes to address false positives, with reasoning and risk assessment accompanying each suggested change. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation. Alert Actions can trigger ControlScripts in response to system events, enabling automated remediation responses to detected conditions in place of manual administrator intervention.
-For platform-level vulnerabilities in the Avi Controller and Service Engines, Avi supports patch application and rollback. After upgrading to a new version, old root partitions that may contain packages with known CVEs can be removed to reduce residual exposure. If a patch introduces instability, rollback features allow operators to return the Controller and all Service Engine groups to the prior version via CLI commands (rollback system, rollbackpatch system) or the REST API (POST api/rollback). The REST API also supports non-disruptive SE-group-specific rollback, allowing selective rollback of individual Service Engine groups. Organizations can lock the Avi Controller Linux system to a specific OS version to avoid CVE scanner false positives from inactive, unused package versions.</t>
+          <t>The Avi Load Balancer Controller is the central management plane for patching and upgrading all components in an Avi Load Balancer deployment. Through the Controller's administration interface, operators can apply patches and upgrades to the Controller cluster and all Service Engine groups from a single point of control via the UI, API, or CLI.
+Patch delivery follows a cumulative model: fixes accumulate within a patch family such that each successive patch release includes all prior fixes (for example, patch 1p2 contains all fixes from 1p1 plus new fixes unique to 1p2, and patch 1p3 includes fixes from both 1p1 and 1p2), and all patches from a maintenance release are incorporated into successive maintenance releases. This means administrators do not need to apply intermediate patches sequentially when updating to a later release within the same family.
+In 9.1, patch delivery can be scoped to specific Service Engine groups based on SE group segmentation, so patches are applied only to the applications or groups that require them. This supports controlled rollout in environments where different workloads have different patch urgency or maintenance windows. The upgrade process also supports a disruptive mode with parallel Service Engine patching, which can reduce patch duration in non-production environments or within scheduled outage windows.
+When a patch rollback is needed, the Avi for VCF documentation provides a structured approach for planning a remediation strategy before re-attempting an upgrade. For concurrent patch operations, the API recommends using GET/PUT workflows rather than PATCH operations to surface concurrent update conflicts rather than silently overwriting earlier updates.
+Alert Actions can trigger ControlScripts in response to system events, enabling automated remediation actions rather than requiring manual administrator intervention. Organizations using infrastructure-as-code tooling can work with Avi's Ansible modules, which automatically handle error reporting and retries, with failures logged and managed gracefully within automation workflows.</t>
         </is>
       </c>
     </row>
@@ -1990,95 +1977,57 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>VCF provides secure baseline configurations for all major platform components, consistent with industry-accepted hardening standards. The VCF Security Baseline is a purpose-built document that builds on VCF security fundamentals to address frequently requested compliance standards, regulations, and frameworks. It is designed and validated to tailor security configurations without affecting VCF's ability to meet its design objectives. Organizations can use the VCF Security Baseline to evaluate both default and non-default configurations and to secure their environments in a compliance context.
-VCF Operations includes a consolidated out-of-the-box benchmark called the VCF 9 Security Baseline, which provides a ready-to-use compliance profile for evaluating the security posture of a VCF environment. This benchmark enables automated assessment of configurations against the documented baseline, helping maintain a consistent configuration across VCF components. ISO Security Standards compliance benchmarks are also available from the VCF Operations repository as a native pack, giving organizations the ability to measure their environment against internationally recognized hardening standards. Broadcom also provides DISA Security Technical Implementation Guides (STIGs) for VCF components, including vSphere 7.0 and vSphere 8.0 STIGs, which provide detailed instructions for securing and configuring systems to meet specific security requirements.
-Individual VCF components have their own security configuration guides that document hardening recommendations. The vSphere Security Configuration Guide provides best practices for securing VMware vCenter, including securing the installation, configuring access and authentication, defining roles and permissions, and enabling auditing and logging. VMware ESX host hardening covers authentication and authorization settings, disabling unnecessary services, enabling security features such as Secure Boot and Trusted Platform Module (TPM), and implementing network security measures. The vSphere Security Configuration Guide documents specific STIG-aligned values for the Security.PasswordQualityControlPwquality setting on ESX hosts, including parameters such as minlen=15, maxrepeat=3, maxclassrepeat=4, difok=4, and enforce_for_root. The NSX Security Configuration Guide provides recommendations for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes, by configuring strong authentication, implementing role-based access control, and securing administrative access.
-VCF Operations also provides a Configure Host Security Config Data workflow that allows selective enforcement of host security hardening rules. Beyond security settings, vSphere Lifecycle Manager maintains a desired-state cluster image that defines the ESX base build, vendor add-ons, and firmware for every host in a cluster, so the software baseline stays consistent across hosts, and VCF Operations runs scheduled drift detection that flags configuration deviations from the desired state for remediation. Administrators can configure individual configuration elements under Enforce Options, enabling granular control over which baseline settings are applied and enforced across the environment. This supports reducing organizational and business risk by maintaining configuration consistency. vSphere Host Profiles provide an additional mechanism for automated and centrally managed host configuration baseline enforcement, capturing a reference host's configuration and applying it consistently across ESX hosts, covering memory, storage, networking, and other configuration aspects.
-For containerized workloads, VMware Kubernetes Service (VKS) includes preconfigured security policy templates. The Baseline security template provides a set of constraints that restrict known privilege escalations while maintaining compatibility with common containerized workloads.
-DISA STIGs for Supervisor and VKrs are available to guide hardening of the Supervisor control plane and individual VKS cluster releases, providing baseline security guidance at the same standard as the DISA STIGs applied to VCF infrastructure components. The VKS cluster management interface provides out-of-the-box security policy templates that mirror industry-standard Pod Security Standards profiles, including both Baseline and Restricted configurations. Custom VKS Cluster Management Security Policy templates are also available to fine-tune individual security context parameters and support governance controls tailored to specific organizational requirements.
-Pod Security Admission (PSA), enabled in VKr 1.25 and later, enforces pod security standards at the namespace level. Three policy profiles are defined: Privileged (unrestricted, for system-level workloads), Baseline (helps prevent known privilege escalations while allowing the default minimally specified pod configuration), and Restricted (heavily restricted, following pod hardening best practices). Three enforcement modes are available: enforce, warn, and audit. The podSecurityStandard field in the ClusterClass API encodes the intended security posture in cluster definitions, accepting these modes with specific policy versions and namespace exemptions so that baseline security configurations are applied consistently across VKS deployments. System namespaces including kube-system, tkg-system, and vmware-system-cloudprovider are excluded from pod security enforcement. The PSA admission controller can also be statically configured with default enforce, audit, and warn levels for unlabeled namespaces, so namespaces created without explicit labels still receive a defined security baseline. To support gradual policy adoption, audit and warn modes can be set to a stricter level such as restricted while enforce remains at baseline, giving administrators visibility into policy violations before full enforcement is applied. VCF Automation IaaS Resource Policies provide an additional enforcement point at the management layer, supporting requirements that Kubernetes clusters operate at a minimum baseline pod security level.
-Kubernetes-native kernel security mechanisms provide workload-level baseline hardening options. seccomp restricts the Linux kernel system call surface available inside containers using BPF-based profiles, and the RuntimeDefault seccomp profile provides a strong set of security defaults while preserving workload functionality. AppArmor and SELinux provide further kernel-level restrictions through default configurations that offer foundational protections. Kubernetes default RBAC role bindings should be reviewed as part of establishing a security baseline, as defaults may grant broader access than a hardened configuration requires. Isolating each workload in its own Kubernetes namespace allows tailored security policies to be applied per workload and restricts access to namespace-scoped resources such as ConfigMaps and Secrets.
-Harbor Registry, available as a standard package for VKS clusters, supports a controlled baseline for container artifacts entering the environment. Harbor provides vulnerability scanning, content trust, and policy-based replication, along with role-based access control and artifact security policies, supporting controlled management of the container image supply chain. For stand-alone virtual machines deployed in vSphere Supervisor environments, Content Libraries can distribute VM images created with current patches and required security settings that follow corporate security policies.
-VMware Private AI Services (PAIS) provides PAIS-specific declarative configuration mechanisms that organizations can use to define and apply baseline settings across the AI infrastructure stack on VCF.
-The primary mechanism is the PAISConfiguration custom resource. Private AI Services settings are declared in a YAML file compliant with the PAISConfiguration schema and applied with kubectl, giving administrators a single resource that captures observability, identity, and trust configuration for an organization namespace. Observability includes the spec.observability.prometheusRuntime section for Prometheus metrics collection with a configurable storage class and metrics retention period, and an llmTraces section for routing large language model traces to an OpenTelemetry Collector. The PAISConfiguration custom resource can be patched with kubectl patch and verified with kubectl get paisconfiguration, supporting baseline change control and drift detection at the AI service layer.
-Certificate trust is handled through the spec.clientTls.caBundleRefs section, which references ConfigMaps containing CA trust bundles. Private AI Services requires HTTPS trust bundles for the OIDC provider, the Harbor registry, content management systems hosting knowledge database data, and MCP servers that provide tools to models. Trust bundles can be organized per application, with periodic updates required before certificate expiration. Access scope is restricted through the authorizedGroups setting, which limits Private AI Services access to specified OIDC groups.
-Harbor registry distribution carries baseline controls for model and image artifacts. Replication rules support configurable filters, target namespace, and trigger mode, including a manual trigger mode, so administrators can align artifact replication with organizational policy for connected and disconnected sites. The Model Gallery uses Harbor project access capabilities to restrict access to sensitive training and tuning data. Air-gapped deployments capture the self-hosted registry URL and registry login credentials as part of the activation flow.
-Workload resource baselines are defined through SupervisorNamespaceClassConfig, which specifies per-zone CPU limits, CPU reservations, memory limits, and memory reservations for resource allocation across zones. GPU-capable VM classes can carry GPU reservations and be confined to a single zone or supervisor namespace, supporting isolation of GPU consumption to a specific tenant. A default storage policy selection in the Private AI Services quickstart defines storage placement and resources for the service database.
-Deep Learning VM (DL VM) baselines are captured through VCF Automation self-service catalog items that parameterize VM class, data disk size, user password, and optional SSH public key authentication for remote access. The DL VM OVF property config-json accepts a base64-encoded configuration file that controls DCGM Exporter metrics visibility through export_dcgm_to_public and JupyterLab authentication through enable_jupyter_auth, giving operators a consistent surface to define DL VM hardening parameters.
-Credentials supplied during Private AI Services activation, including the private container registry password and proxy password, are stored as secrets in VCF Automation rather than as plaintext configuration values, supporting credential hygiene as part of the deployment baseline.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to secure baseline configurations within its network security domain by providing structured configuration management capabilities, predefined security profiles and strategies, and configuration integrity controls that align with industry-accepted hardening practices.
-vDefend supports draft configuration management with configuration locking to prevent multiple users from simultaneously opening and editing a manual draft, helping maintain configuration integrity and reducing the risk of conflicting changes to firewall policy. Role-Based Access Control (RBAC) in vDefend governs who can create or modify firewall policies, providing control over which administrators can alter the security baseline.
-In vDefend, five system-defined VPC Security Strategies are available for establishing security baselines across Virtual Private Clouds (VPCs): VPC Isolation, VPC Isolation with Essential Services, VPC External Connectivity, VPC Secure Connection, and NONE. These strategies are consumed through Security Profiles in VCF Automation, which are predefined configuration templates that define the default security posture for VPCs. VPC Security Strategies provide a declarative, consistent way to apply DFW security baselines across multiple VPCs within a project, and Project Admins are guided to select a pre-defined high-level security posture that enforces Secure by Default principles rather than manually configuring individual firewall rules. Security profiles can be applied to one or more VPCs simultaneously and updated as requirements evolve.
-vDefend provides predefined TLS Decryption Action Profiles with four settings: Balanced (default), High Fidelity, High Security, and Custom. These profiles are vendor-defined baseline configurations for TLS inspection behavior, giving organizations a documented starting point aligned with different security postures. TLS Inspection policies also support an Advanced Configuration option to lock policies, preventing multiple users from making concurrent changes to TLS inspection policy baseline settings.
-Security Services Platform validates configuration changes before implementation through a deployment wizard that conducts thorough validations to confirm configurations are correct and compatible. The platform enforces initial security policies that cannot be modified through the user interface after they have been published, providing an immutability mechanism for foundational policy baseline elements. Security Services Platform supports backup and restore of configuration data, and certificate consistency between backup and restored environments should be verified to maintain NDR sensor integrity.
-Security Services Platform's Bare Metal Security feature extends vDefend policy enforcement to physical servers, applying L3/4 security policies to bare metal infrastructure using the same policy model and management plane as virtualized workloads. Two default DFW rules are created when Bare Metal servers are onboarded to Security Services Platform, providing an immediate baseline posture for physical infrastructure. Security policies are defined, propagated, and enforced across Bare Metal servers with consistent application and monitoring.
-vDefend's configuration management capabilities operate within the network security layer. The broader secure baseline configuration program for VCF, including the VCF Security Baseline document, component hardening guides, DISA STIGs, and compliance scanning through VCF Operations, is managed at the platform level. vDefend contributes by maintaining its own secure defaults and configuration controls within the network security domain.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides configurable security baseline mechanisms for its replication and recovery infrastructure. The PNR appliance includes a security reference section that identifies configuration files containing settings that affect environment security, and PNR documentation establishes that secure operation depends on proper configuration and maintenance of the PNR server. The security reference also documents network port requirements, providing the technical specifications needed to develop and maintain secure baseline configurations for disaster recovery infrastructure.
-PNR includes a Configuration Import/Export Tool that captures the complete set of protection and recovery configuration settings, including server version, build number, local and remote site names, inventory mappings, placeholder datastores, advanced settings, and array managers. The tool supports both UI-based and scripted exports and can transfer configuration data without requiring credential entry when using the bundled generated script. This gives organizations a mechanism to document, back up, and restore known-good baseline configurations for their disaster recovery infrastructure. The underlying system configuration is stored in the va-configurator.xml file and is accessible through Advanced Settings on the Site Pair tab in the management interface, providing a defined location for baseline review and modification.
-The PNR appliance management interface allows administrators to configure appliance security settings after deployment. The Advanced Settings system provides privileged users with the ability to adjust default values governing protection and recovery features. When modifying the minimum protocol version for TLS, PNR requires that the change be applied consistently across all configuration occurrences in the system, supporting systematic baseline management for transport security settings.
-For cyber recovery deployments, PNR documentation recommends using standard VCF topology with separate workload and management domains to achieve better isolation and align with security best practices at the recovery site.
-Full compliance with this control requires an organizational baseline configuration management program, documentation practices, version control, and hardening tooling extending beyond what PNR provides directly.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to secure baseline configuration management through its infrastructure policy framework, data service policy enforcement, and built-in secure defaults for authentication and certificate management.
-Infrastructure policies in DSM define the compute, storage, and networking resources for each database deployment, including the list of allowed VM classes and compatible storage policies. These policies are configured by DSM administrators and act as standardized, repeatable deployment baselines that database users must follow. When administrators configure infrastructure policies, they constrain the quality and quantity of resources that users can consume from vSphere clusters, establishing guardrails that support consistent deployments across the environment. Database cluster creation applies both infrastructure policies and storage policies that enforce isolation and resource constraints, reducing the risk of misconfiguration by individual users.
-Data service policies extend this baseline enforcement across multi-tenant deployments. DSM administrators can define and configure data service policies for various database services and enforce them across different tenants to maintain a consistent security and compliance posture. Data service policies constrain which infrastructure options can be applied to database instances. When DSM is integrated with VCF Automation, data service policies can be applied consistently across organizational units.
-DSM also ships with predefined secure defaults for database authentication. PostgreSQL databases on DSM use scram-sha-256 as the default password-based authentication method, as configured in the default pg_hba.conf entries stored at /pgsql/data/pg_hba.conf. Custom pg_hba.conf entries support scram-sha-256, reject, and cert authentication methods. TLS is enforced by default for database client connections, with an administrator-controlled option to relax enforcement via the postgrescluster-allow-non-ssl-system-users setting in the advanced-system-config ConfigMap within the dsm-system namespace.
-Certificate management is integrated into the database creation workflow and validates certificate chains for connections to external systems, including VMware vCenter. DSM introduces a stricter default certificate validation mode, the "latest" mode, that enforces cryptographic and KeyUsage validations for all DSM endpoints, including the Provider VM and data service clusters. Certificates uploaded to DSM are validated against FIPS 140-3 cryptographic standards, and uploads containing unsupported algorithms or parameters are rejected. Custom trusted root certificates must comply with FIPS requirements. DSM also verifies the SHA256 thumbprint of vCenter during initial configuration to confirm the management connection targets the expected endpoint. Custom certificate support allows organizations to replace the default DSM certificate with organization-issued certificates for both the Provider VM and database clusters. For self-service deployments using the DSM Consumption Operator, signature verification confirms package integrity before installation.
-DSM validates certificate chains using configured root CA certificates stored in ConfigMaps and supports private container registry configuration with CA certificate validation for air-gapped environments.
-Addressing this control fully requires organizational processes beyond what DSM provides directly. DSM does not include tooling to document baseline configurations in a compliance-ready format, map configurations to specific industry hardening standards, or audit deviations from defined baselines over time. Organizations should supplement DSM's policy and defaults framework with configuration management documentation, change tracking processes, and integration with compliance scanning tools to satisfy the full requirements of this control.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several built-in mechanisms that support the development and application of secure baseline configurations for the application delivery layer.
-The SSL/TLS Profile system gives administrators a documented starting point for cryptographic configuration. Profile Templates define accepted SSL and TLS versions and ciphers in prioritized order, and can be associated with virtual services or the Controller itself. The Standard SSL/TLS Profile is suitable for typical deployments, while the System-Standard profile provides modern cipher suites for backend server re-encryption in Kubernetes environments managed through the Avi Kubernetes Operator (AKO). Avi includes a curated list of cipher suites considered reasonably strong for SSL/TLS configuration, and the documentation notes the trade-offs between security, compatibility, and computational expense when selecting profiles. The Service Engine disables unsafe legacy renegotiation by default, providing a built-in protocol hardening baseline that reduces the risk of protocol downgrade attacks.
-The System-Secure-HTTP application profile is a pre-configured baseline for securing HTTP virtual services. It enforces HTTPS, protects cookies, manages client IP handling, and controls protocol behavior, giving administrators a hardened starting point for web application delivery. Administrators can supplement these defaults with more granular settings through policies or DataScripts.
-For deployments requiring validated cryptographic modules, Avi Load Balancer implements FIPS 140-3 compliance, providing a cryptographic baseline aligned with the U.S. and Canadian government standard for cryptographic modules.
-The Avi Web Application Firewall (WAF) Positive Security model supports application-layer baseline configuration through rules that define allowed application behavior. Each rule supports Enable/Disable control, mode selection between Detection and Enforcement, and configurable Paranoia levels, allowing organizations to tune an application security baseline to their risk posture. The Positive Security Rule Updates feature can be enabled to activate additional configuration options for application security policies. The Cloud Console Application Rules service extends this with rules specifically designed to address known application vulnerabilities, including those with CVEs, and updates them automatically.
-For Kubernetes deployments, AKO uses Custom Resource Definitions (CRDs) to enable syntactical validation of configuration objects at creation time, which helps prevent invalid configurations from being deployed. The AKO L4 CRD Rule supports SSL profiles and PKI profiles for securing pool connections, allowing Kubernetes-native expression of Avi's cryptographic baseline settings.
-Certificate lifecycle management supports maintaining cryptographic baselines over time. Certificate Management Profiles support automated certificate renewal workflows, and the Trust Protection Platform integration can automatically handle certificate and chain certificate renewals by learning the mapping of virtual service names to their certificates.
-The organizational process of developing, documenting, and maintaining baseline configurations across all in-scope technology assets, including selecting appropriate profile settings, applying them consistently, and updating them as software versions and security guidance evolve, remains outside what Avi performs on the organization's behalf.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -2102,54 +2051,37 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>VCF provides technical capabilities that support several phases of the incident handling lifecycle, though the organizational preparation, process governance, and manual intake elements require processes and structures outside the platform.
-For preparation, VCF Operations supports the configuration of notification rules with detailed incident field mappings, including incident state, resolution codes, impact, urgency, priority, severity levels, and assignment groups. The ServiceNow Management Pack can be configured with parameters such as callerId, propagateAlertUpdates, retrieveIncidentUpdates, and incidentReopenState, allowing organizations to establish incident handling workflows before events occur. These configuration options allow teams to define how incidents are categorized, prioritized, and routed in advance of any actual incident.
-For automated event detection, VCF Operations correlates events from monitored infrastructure components and delivers them as faults. Events are ranked by severity from Info through Warning, Critical, and Immediate, and notification rules trigger actions based on incident state changes. VCF Operations can automatically create incidents in ServiceNow through the Service-Now Notifications plug-in, with structured information including the caller, category, subcategory, and business service. This integration bridges the gap between infrastructure monitoring and organizational incident tracking systems. VCF Operations also combines Diagnostic Findings with VCF Health to detect and predict issues, which helps reduce mean time to resolution. VMware vCenter alarms provide additional automated detection, triggering script execution, SNMP traps, email notifications, or API calls when infrastructure conditions exceed defined thresholds.
-For analysis, the Troubleshooting Incident Page displays information related to the entity under investigation, including traffic and flows on the entity, past incidents created for that entity, status, root cause metrics, and closing remarks. Operators can flag metrics and mark specific metrics as root cause during investigation. The Notes section on each incident allows users to add observations that are visible to anyone who opens the session, which supports collaborative analysis across team members. vCenter Events record user and system actions on inventory objects and can be used for forensic analysis and auditing of activity in the virtual environment, providing an audit trail for incident investigation. Diagnostic Findings consolidates log-based and property-based findings with specific resolution recommendations and links to knowledge base articles, helping analysts identify known issues by matching log patterns and property-based signatures against a library of diagnostic rules. Log Assist can generate log bundles and automatically attach property-based diagnostic findings data to support cases. VCF Operations also integrates with ServiceNow, allowing incidents to flow into existing ITSM workflows for structured triage.
-For containment, vCenter supports isolating affected workloads through VM power state changes and network reconfiguration. VMware vDefend (a separate product that extends VCF's networking foundation) provides more targeted containment through quarantine policies that automatically isolate VMs based on security events while preserving forensic access for investigation. Physical containment, network isolation decisions, and cross-system coordination during active incidents depend on processes and authority structures that exist outside the platform.
-For eradication, VCF Operations maps out-of-the-box workflows to recommendations and associates them with specific alerts, enabling automated remediation of known conditions. Diagnostic Findings helps operators find and resolve known issues using diagnostic rules and signatures, with recommended fixes based on industry-standard best practices.
-For recovery, vSphere HA automatically restarts VMs on healthy hosts after a host failure, with admission control policies that reserve capacity for failover. Proactive HA integrates with hardware vendor monitoring to detect degrading components and evacuate workloads before failure occurs. vSphere Fault Tolerance provides continuous availability for workloads that require zero-downtime protection during failover. VCF Operations maintains a summary view of all incidents with status tracking, entity counts for in-progress incidents, and counts of top root causes for visibility into the overall state of incident resolution.
-VCF Operations also provides a centralized incident list displaying all incidents with their status and key details, with edit, share, and delete actions for incident lifecycle management. Incident tracking captures state, resolution code, resolution notes, impact (business criticality), urgency (resolution timeframe), priority (resolution sequence), severity level, and approval workflow documentation, which is a structured audit trail for each incident. The Guided Network Troubleshooting feature automatically maintains a list of the 20 most recently modified incidents within a selected scope for continuity across investigation sessions.
-While VCF Operations provides tooling for detection, analysis, and remediation of infrastructure incidents, several aspects of the six-phase incident handling lifecycle require organizational processes beyond what the platform provides. Preparation requires documented incident response plans, team roles, and communication procedures. Manual incident report intake requires organizational channels and triage processes. Containment decisions require human judgment and authority structures. A formal incident response program that incorporates VCF's technical capabilities into broader organizational processes is necessary to address all six phases.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides technical mechanisms that support the recovery, containment, and detection phases of incident handling through recovery plans, isolated cyber-recovery workflows, structured event logging, and integration with security monitoring platforms.
-Recovery plans define ordered procedures for recovering protected workloads at a recovery site, including custom recovery steps. PNR handles custom command failures in recovery plans based on the type of command, allowing operators to control how the plan continues when steps fail. When a disaster event affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so that users can recover workloads. After execution, PNR provides the ability to view and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup, producing documented evidence for after-action review.
-For containment and eradication, the Clean Room Orchestrator enables triage and analysis of recovered workloads in an isolated environment. PNR monitors a global collection of clean room events, tasks, and alarms for recovery operations, with Clean Room Orchestrator events classified at severity levels of Info, Warning, Error, and Emergency. This isolated environment supports analysis of suspect workloads in parallel to site-level recovery actions.
-For detection and analysis, PNR logs events and triggers corresponding alarms to track system health, with event records including timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type. PNR tracks Site Status events that provide information about the status of protected and recovery sites and the connection between them. PNR can forward Clean Room Orchestrator events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, supporting integration with broader security monitoring and incident response platforms.
-PNR Health findings classify status into Error, Warning, and Info categories and are visible through Protection and Recovery dashboards in VCF Operations. Deployment topology with separate management domains for each region is designed to contain the impact of a disaster event to one particular region, supporting preparation by limiting blast radius.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
@@ -2164,18 +2096,12 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>Avi Load Balancer contributes to the incident handling lifecycle by providing application-layer detection, analysis, automated alerting, and recovery capabilities within its role as an application delivery controller.
-For preparation, the Controller's alert and event framework supports pre-configured response actions. ControlScripts, defined under Alert Actions in the Controller UI, allow administrators to specify automated responses that fire when defined alert conditions are met. The Alert feature processes system events and metrics against user-defined rules and generates notifications via email, syslog message, or SNMP trap. The Syslog-Audit-Persistence alert action streams audit compliance events to external syslog servers, enabling incident response tooling to receive Avi event data in real time.
-For automated event detection, the Controller's System Events Overlay records event codes that provide high-level definitions of system status, including SERVER_HEALTH_DEGRADED, POOL_HEALTH_DEGRADED, and VS_UP. The Avi Service Engine logs events when WAF matches a transaction, and logs audit record failures to Events, Syslog, and Splunk, covering initiation and termination of trusted channels, certificate validation failures, client authentication failures, and SSH session establishment failures. The Application Security Report provides an executive summary alongside WAF statistics, including ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking source IP addresses, and trend summaries of total and flagged request volumes.
-For analysis, Avi Service Engine health monitoring records failure details for each monitored server, including failure type, failure count, average response time, and minimum and maximum response times. The Service Engine analytics page displays the list of failed health monitors per server in a pool, enabling investigation of health patterns. WAF Log Analytics supports creation of exceptions at the group or rule level for false positive remediation, enabling more accurate signal analysis during an investigation. Support bundles collect diagnostic data, logs, and configuration information from the system to assist in troubleshooting and resolving issues.
-For containment, WAF policies block application-layer requests that match defined rules or anomaly score thresholds, and WAF Policies can attach a Positive Security group to apply learned data and define hit/miss actions for fine-grained control. ControlScripts can trigger automated containment actions in response to alert events.
-For recovery, the Avi for VCF rollback procedure supports validation of the operational status of all VIPs and pools, followed by end-to-end health checks on the VS-App environment. GSLB services with the priority algorithm support a manual resume option for controlled failover and recovery management.
-The full incident handling program, including organizational preparation procedures, eradication processes for removing attacker footholds across the broader environment, cross-team coordination, and end-to-end recovery governance, requires processes and tooling beyond what Avi provides within its application delivery scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2355,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -2444,18 +2370,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides structured classification and prioritization mechanisms for security detection events within the network security domain.
-Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help security teams prioritize response actions. Security Intelligence also categorizes detected events by MITRE adversarial tactics and techniques, recording occurrence counts during the selected time period, which provides additional context for classification decisions.
-Network Detection and Response (NDR) assigns impact scores to campaigns, with higher scores indicating higher priority for triage and response. Detection events are classified into impact levels; events with an impact score from 1 to 24 are classified as Informational, indicating the detected activity is not essentially malicious. NDR calculates impact scores from Confidence and Severity values, and contextual scoring logic may promote some Informational detections to a higher impact level. NDR also provides filtering of the unified event list by detection impact score using checkboxes, which allows security teams to focus investigation on higher-priority detections.
-The Security Services Platform (SSP) Campaign view includes a Blueprint tab that visualizes correlated security events and key actors, supporting investigation of multi-stage incidents. Security teams can investigate individual threat events and correlated campaigns through the SSP interface to assess impact, identify root causes, and take appropriate mitigation actions.
-VMware vDefend includes an Intelligent Assist triage capability: when responding to security incidents, security teams can select a Targeted Strategy for surgical, safer remediation with potentially lower effectiveness, or a Comprehensive Strategy for broader remediation with potentially lower safety. This capability helps match remediation scope to assessed incident severity.
-IDS/IPS events are classified by severity level (Informational, Low, Medium, High, and Critical), and vDefend IDS/IPS follows a prioritized event-handling approach under memory pressure, dropping non-critical severity data (Low and Informational) first, followed by Medium, then High and Critical severity events, with packet captures dropped only as a last resort. This built-in severity hierarchy reflects the product's internal classification model.
-The broader incident classification process, including establishing organizational incident categories, defining triage protocols, and coordinating business continuity actions, remains an organizational function that extends beyond network-layer detection capabilities.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
